--- a/assets/templates/inventory-balance-match/opening.xlsx
+++ b/assets/templates/inventory-balance-match/opening.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Aleman\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\برنامج مراجعة المخازن\Templetes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{959CEA2C-CCE6-417A-B904-55A1E594750C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6B9D2FC-8699-4481-B9CB-6ADA1E4E0F3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,10 +25,10 @@
     <t>كود الصنف</t>
   </si>
   <si>
-    <t>وحدة القياس</t>
+    <t>وصف الصنف</t>
   </si>
   <si>
-    <t>الرصيد الإفتتاحي</t>
+    <t>رصيد SAP</t>
   </si>
 </sst>
 </file>
@@ -78,7 +78,7 @@
   </cellStyles>
   <dxfs count="5">
     <dxf>
-      <protection locked="1" hidden="1"/>
+      <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
       <protection locked="0" hidden="0"/>
@@ -90,7 +90,7 @@
       <protection locked="0" hidden="0"/>
     </dxf>
     <dxf>
-      <protection locked="0" hidden="0"/>
+      <protection locked="1" hidden="1"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
@@ -106,12 +106,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D880D8E-DCB0-44F4-BEDB-7EB831F5D862}" name="Table1" displayName="Table1" ref="A1:C100" totalsRowShown="0" headerRowDxfId="0" dataDxfId="1">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{4D880D8E-DCB0-44F4-BEDB-7EB831F5D862}" name="Table1" displayName="Table1" ref="A1:C100" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="A1:C100" xr:uid="{4D880D8E-DCB0-44F4-BEDB-7EB831F5D862}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{EB7D4464-D9D3-46D6-B731-AF83BAC20797}" name="كود الصنف" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{CC398CE0-C06E-4AB0-A109-79390B90734A}" name="وحدة القياس" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{F4B9F851-AD9C-411F-AF6A-E1EEE6AE3F0D}" name="الرصيد الإفتتاحي" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{EB7D4464-D9D3-46D6-B731-AF83BAC20797}" name="كود الصنف" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{CC398CE0-C06E-4AB0-A109-79390B90734A}" name="وصف الصنف" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{F4B9F851-AD9C-411F-AF6A-E1EEE6AE3F0D}" name="رصيد SAP" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -440,15 +440,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.796875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="11.69921875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="38.796875" style="1" customWidth="1"/>
     <col min="3" max="3" width="13.796875" style="1" customWidth="1"/>
     <col min="4" max="16384" width="8.796875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -460,7 +460,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="AiAkoCyxJIVp0wnyn6JVl/cfJw/52ybBadhW0EMnUwJlRGKa7ylK/ocY51V4+FxM8ZQ3nJSuPpu0KsMObODoSQ==" saltValue="HGcN5xBp0pf9y0Hlzho8VQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="AMoHLrvw7k3B2jraxeAtJbVbTIS0bRZj5peLVkk7Xa91ctZqcoVwFFiLqQu6VUWnj0H6X5+aRfSeV07XuO+axA==" saltValue="3yPqobGKF3QaI2Swu774kw==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <tableParts count="1">
     <tablePart r:id="rId1"/>
